--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.105.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.105.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.105.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.105.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="51" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.105.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.105.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0105.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0105.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -605,22 +605,30 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: (30)ã€‚</t>
+          <t>L43: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | symbol-only separator/garbage line :: (30)。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: THE MASTERâ€™S OFFICE.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]98</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]98</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: symbol-only separator/garbage line :: (20).</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr"/>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]98</t>
+        </is>
+      </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
@@ -645,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -656,7 +664,7 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L137: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: (37)ã€‚</t>
+          <t>L137: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | symbol-only separator/garbage line :: (37)。</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr"/>
@@ -750,7 +758,7 @@
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L48: symbol-only separator/garbage line :: (39).</t>
+          <t>L43: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | symbol-only separator/garbage line :: (30)。</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr"/>
@@ -793,7 +801,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L53: symbol-only separator/garbage line :: (49).</t>
+          <t>L48: symbol-only separator/garbage line :: (39).</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -836,7 +844,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: B</t>
+          <t>L53: symbol-only separator/garbage line :: (49).</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -879,7 +887,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L98: symbol-only separator/garbage line :: (50).</t>
+          <t>L95: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -922,7 +930,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L104: symbol-only separator/garbage line :: (59).</t>
+          <t>L98: symbol-only separator/garbage line :: (50).</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -965,7 +973,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L127: isolated marker/symbol line :: . 5</t>
+          <t>L104: symbol-only separator/garbage line :: (59).</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -993,7 +1001,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1008,7 +1016,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L142: isolated marker/symbol line :: A</t>
+          <t>L127: isolated marker/symbol line :: . 5</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1031,12 +1039,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1049,7 +1057,11 @@
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
-      <c r="N12" s="1" t="inlineStr"/>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>L137: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | symbol-only separator/garbage line :: (37)。</t>
+        </is>
+      </c>
       <c r="O12" s="1" t="inlineStr"/>
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr"/>
@@ -1088,7 +1100,11 @@
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
-      <c r="N13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>L142: isolated marker/symbol line :: A</t>
+        </is>
+      </c>
       <c r="O13" s="1" t="inlineStr"/>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
